--- a/EXCEL/Exercise Files/Chapter01/01_01_Means.xlsx
+++ b/EXCEL/Exercise Files/Chapter01/01_01_Means.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Writing\Lynda\Data Analysis Fundamentals 20220331 Refresh\Exercise Files\Chapter01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E33F511-943F-4501-BFDD-F82331552180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EECD0B7-5E1D-45A4-84F8-07ACCDA4C894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="45" windowWidth="25575" windowHeight="21555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,32 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -376,81 +397,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <f>AVERAGE(A2:A12)</f>
+        <v>29.454545454545453</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f>MEDIAN(A2:A12)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f>_xlfn.MODE.SNGL(A2:A12)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">_xlfn.MODE.MULT(A2:A12)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>37</v>
       </c>
